--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487771_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487771_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3114</v>
+        <v>5.4125</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8118</v>
+        <v>4.9423</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4995</v>
+        <v>0.4702</v>
       </c>
       <c r="G2" t="n">
         <v>4.8221</v>
@@ -610,13 +610,13 @@
         <v>1.0406</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9016</v>
+        <v>-0.8005</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5004999999999999</v>
+        <v>-0.37</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4011</v>
+        <v>-0.4305</v>
       </c>
       <c r="V2" t="n">
         <v>0.3503</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0374</v>
+        <v>2.7269</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7556</v>
+        <v>3.8268</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7181999999999999</v>
+        <v>-1.0998</v>
       </c>
       <c r="G3" t="n">
         <v>4.0873</v>
@@ -688,13 +688,13 @@
         <v>1.2487</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2836</v>
+        <v>0.9731</v>
       </c>
       <c r="T3" t="n">
-        <v>2.879</v>
+        <v>0.9502</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4046</v>
+        <v>0.0229</v>
       </c>
       <c r="V3" t="n">
         <v>0.5802</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.584</v>
+        <v>0.9722</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.9184</v>
+        <v>-1.8531</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5023</v>
+        <v>2.8253</v>
       </c>
       <c r="G4" t="n">
         <v>0.6159</v>
@@ -766,13 +766,13 @@
         <v>0.4162</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3314</v>
+        <v>0.0568</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.5219</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2558</v>
+        <v>0.5787</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1168</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3501</v>
+        <v>-0.0667</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.432</v>
+        <v>-1.3249</v>
       </c>
       <c r="F5" t="n">
-        <v>1.082</v>
+        <v>1.2581</v>
       </c>
       <c r="G5" t="n">
         <v>0.1265</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1435</v>
+        <v>0.1398</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3915</v>
+        <v>-0.2843</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2479</v>
+        <v>0.4241</v>
       </c>
       <c r="V5" t="n">
         <v>0.7076</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9741</v>
+        <v>-0.8326</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3595</v>
+        <v>0.1343</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6146</v>
+        <v>-0.9669</v>
       </c>
       <c r="G6" t="n">
         <v>2.0125</v>
@@ -922,13 +922,13 @@
         <v>1.2487</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9831</v>
+        <v>-0.8416</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0191</v>
+        <v>-0.5252</v>
       </c>
       <c r="U6" t="n">
-        <v>0.036</v>
+        <v>-0.3163</v>
       </c>
       <c r="V6" t="n">
         <v>-1.1711</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.884</v>
+        <v>-3.0971</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.8524</v>
+        <v>-5.5076</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9684</v>
+        <v>2.4106</v>
       </c>
       <c r="G8" t="n">
         <v>-2.6401</v>
@@ -1078,13 +1078,13 @@
         <v>0.4162</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9611</v>
+        <v>0.748</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7177</v>
+        <v>-0.3729</v>
       </c>
       <c r="U8" t="n">
-        <v>1.6787</v>
+        <v>1.1209</v>
       </c>
       <c r="V8" t="n">
         <v>0.4599</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. MARINA PARRA</t>
+          <t>A. PALAZUELOS PEREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.5853</v>
+        <v>-5.3733</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.5672</v>
+        <v>-3.1824</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0181</v>
+        <v>-2.1909</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3402</v>
+        <v>-1.5616</v>
       </c>
       <c r="H9" t="n">
+        <v>-0.6905</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.8711</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-1.8961</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-2.3394</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.4433</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.6489</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-1.3144</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-1.0406</v>
       </c>
-      <c r="I9" t="n">
-        <v>-0.2996</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-0.8829</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-0.7955</v>
-      </c>
-      <c r="L9" t="n">
-        <v>-0.08740000000000001</v>
-      </c>
-      <c r="M9" t="n">
-        <v>-0.4573</v>
-      </c>
-      <c r="N9" t="n">
-        <v>-0.245</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-0.2123</v>
-      </c>
-      <c r="P9" t="n">
-        <v>-3.9542</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-4.1624</v>
-      </c>
       <c r="R9" t="n">
-        <v>0.2081</v>
+        <v>1.0406</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1233</v>
+        <v>-1.2431</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5219</v>
+        <v>-0.2457</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3986</v>
+        <v>-0.9974</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1675</v>
+        <v>-2.5686</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1675</v>
+        <v>-2.5686</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. PALAZUELOS PEREZ</t>
+          <t>N. MARINA PARRA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.6459</v>
+        <v>-6.1692</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.9558</v>
+        <v>-5.1805</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.69</v>
+        <v>-0.9887</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5616</v>
+        <v>-1.3402</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6905</v>
+        <v>-1.0406</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8711</v>
+        <v>-0.2996</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.8961</v>
+        <v>-0.8829</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.3394</v>
+        <v>-0.7955</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4433</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3345</v>
+        <v>-0.4573</v>
       </c>
       <c r="N10" t="n">
-        <v>1.6489</v>
+        <v>-0.245</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3144</v>
+        <v>-0.2123</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-3.9542</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0406</v>
+        <v>-4.1624</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0406</v>
+        <v>0.2081</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.5157</v>
+        <v>0.2928</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0191</v>
+        <v>-0.1352</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.4966</v>
+        <v>0.428</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.5686</v>
+        <v>-1.1675</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.5686</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.1408</v>
+        <v>-9.567600000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-9.7118</v>
+        <v>-9.4323</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.429</v>
+        <v>-0.1354</v>
       </c>
       <c r="G11" t="n">
         <v>-4.1067</v>
@@ -1312,13 +1312,13 @@
         <v>1.4568</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1306</v>
+        <v>-0.5575</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1743</v>
+        <v>0.1053</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9564</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1168</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-18.462</v>
+        <v>-17.8095</v>
       </c>
       <c r="E12" t="n">
-        <v>-19.5389</v>
+        <v>-18.8866</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0769</v>
+        <v>1.0771</v>
       </c>
       <c r="G12" t="n">
         <v>1.9997</v>
@@ -1363,19 +1363,19 @@
         <v>-4.6332</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7742</v>
+        <v>-0.7742000000000009</v>
       </c>
       <c r="K12" t="n">
         <v>-1.1007</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3264999999999998</v>
+        <v>0.3265</v>
       </c>
       <c r="M12" t="n">
         <v>2.7741</v>
       </c>
       <c r="N12" t="n">
-        <v>7.7337</v>
+        <v>7.733699999999999</v>
       </c>
       <c r="O12" t="n">
         <v>-4.9597</v>
@@ -1390,13 +1390,13 @@
         <v>7.284</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.3908</v>
+        <v>-1.7385</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.3785</v>
+        <v>-1.7259</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.01249999999999984</v>
+        <v>-0.01239999999999997</v>
       </c>
       <c r="V12" t="n">
         <v>-3.5027</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. ORENGA IMAZ</t>
+          <t>R. LLAMAS MARTINEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.5087</v>
+        <v>4.984</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9411</v>
+        <v>2.9364</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5677</v>
+        <v>2.0477</v>
       </c>
       <c r="G13" t="n">
-        <v>2.928</v>
+        <v>-0.9229000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>2.1491</v>
+        <v>-0.5033</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7789</v>
+        <v>-0.4196</v>
       </c>
       <c r="J13" t="n">
-        <v>2.1401</v>
+        <v>-0.8411</v>
       </c>
       <c r="K13" t="n">
-        <v>1.4347</v>
+        <v>-0.2051</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7054</v>
+        <v>-0.636</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7879</v>
+        <v>-0.0818</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7144</v>
+        <v>-0.2982</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0735</v>
+        <v>0.2164</v>
       </c>
       <c r="P13" t="n">
-        <v>1.6649</v>
+        <v>1.8731</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6649</v>
+        <v>1.8731</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3758</v>
+        <v>0.8851</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.199</v>
+        <v>0.6287</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5748</v>
+        <v>0.2564</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.4599</v>
+        <v>3.1488</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.1488</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.4599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. LLAMAS MARTINEZ</t>
+          <t>P. ORENGA IMAZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.9149</v>
+        <v>4.2944</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1863</v>
+        <v>1.7267</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7286</v>
+        <v>2.5677</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.9229000000000001</v>
+        <v>2.928</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5033</v>
+        <v>2.1491</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4196</v>
+        <v>0.7789</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.8411</v>
+        <v>2.1401</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2051</v>
+        <v>1.4347</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.636</v>
+        <v>0.7054</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.0818</v>
+        <v>0.7879</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2982</v>
+        <v>0.7144</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2164</v>
+        <v>0.0735</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8731</v>
+        <v>1.6649</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8731</v>
+        <v>1.6649</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.184</v>
+        <v>0.1615</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1214</v>
+        <v>-0.4133</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0626</v>
+        <v>0.5748</v>
       </c>
       <c r="V14" t="n">
-        <v>3.1488</v>
+        <v>-0.4599</v>
       </c>
       <c r="W14" t="n">
-        <v>3.1488</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. AMADASUN</t>
+          <t>A. DOMINGUEZ ESPELT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.672</v>
+        <v>3.4947</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6377</v>
+        <v>0.9407</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0343</v>
+        <v>2.554</v>
       </c>
       <c r="G15" t="n">
-        <v>0.08260000000000001</v>
+        <v>2.1612</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0254</v>
+        <v>-0.6464</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0572</v>
+        <v>2.8077</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7156</v>
+        <v>1.9409</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5196</v>
+        <v>-0.4014</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1959</v>
+        <v>2.3423</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.633</v>
+        <v>0.2203</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4942</v>
+        <v>-0.245</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1388</v>
+        <v>0.4654</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6244</v>
+        <v>1.4568</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7055</v>
+        <v>2.4974</v>
       </c>
       <c r="S15" t="n">
-        <v>3.9026</v>
+        <v>-0.5833</v>
       </c>
       <c r="T15" t="n">
-        <v>3.7734</v>
+        <v>-0.4195</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1292</v>
+        <v>-0.1637</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9376</v>
+        <v>0.4599</v>
       </c>
       <c r="W15" t="n">
-        <v>0.23</v>
+        <v>0.4599</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. HAYMAN</t>
+          <t>E. VAN DER HEIJDEN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.3125</v>
+        <v>3.3973</v>
       </c>
       <c r="E16" t="n">
-        <v>1.474</v>
+        <v>1.7408</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8385</v>
+        <v>1.6565</v>
       </c>
       <c r="G16" t="n">
-        <v>2.8641</v>
+        <v>0.7596000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3219</v>
+        <v>-0.243</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5422</v>
+        <v>1.0026</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9375</v>
+        <v>1.4865</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8974</v>
+        <v>0.2022</v>
       </c>
       <c r="L16" t="n">
-        <v>1.0401</v>
+        <v>1.2842</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9266</v>
+        <v>-0.7269</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4245</v>
+        <v>-0.4452</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5021</v>
+        <v>-0.2817</v>
       </c>
       <c r="P16" t="n">
-        <v>1.4568</v>
+        <v>2.2893</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4974</v>
+        <v>2.2893</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4247</v>
+        <v>0.8083</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5905</v>
+        <v>0.2544</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1657</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5838</v>
+        <v>-0.4599</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.7513</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. DOMINGUEZ ESPELT</t>
+          <t>D. HAYMAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.7177</v>
+        <v>3.2347</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5121</v>
+        <v>1.3668</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2056</v>
+        <v>1.8678</v>
       </c>
       <c r="G17" t="n">
-        <v>2.1612</v>
+        <v>2.8641</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6464</v>
+        <v>1.3219</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8077</v>
+        <v>1.5422</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9409</v>
+        <v>1.9375</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4014</v>
+        <v>0.8974</v>
       </c>
       <c r="L17" t="n">
-        <v>2.3423</v>
+        <v>1.0401</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2203</v>
+        <v>0.9266</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.245</v>
+        <v>0.4245</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4654</v>
+        <v>0.5021</v>
       </c>
       <c r="P17" t="n">
         <v>1.4568</v>
@@ -1780,28 +1780,28 @@
         <v>2.4974</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3603</v>
+        <v>-0.5024999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8482</v>
+        <v>-0.6976</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5121</v>
+        <v>0.1951</v>
       </c>
       <c r="V17" t="n">
-        <v>0.4599</v>
+        <v>-0.5838</v>
       </c>
       <c r="W17" t="n">
-        <v>0.4599</v>
+        <v>1.1675</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. VAN DER HEIJDEN</t>
+          <t>M. DENG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.9725</v>
+        <v>1.4854</v>
       </c>
       <c r="E18" t="n">
-        <v>0.455</v>
+        <v>-0.8882</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5175</v>
+        <v>2.3736</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7596000000000001</v>
+        <v>-3.2025</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.243</v>
+        <v>-2.7208</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0026</v>
+        <v>-0.4817</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4865</v>
+        <v>-2.5737</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2022</v>
+        <v>-2.5165</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2842</v>
+        <v>-0.0572</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7269</v>
+        <v>-0.6289</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4452</v>
+        <v>-0.2043</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2817</v>
+        <v>-0.4245</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2893</v>
+        <v>1.2487</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R18" t="n">
         <v>2.2893</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6165</v>
+        <v>1.1042</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0315</v>
+        <v>0.3911</v>
       </c>
       <c r="U18" t="n">
-        <v>0.415</v>
+        <v>0.7131</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.4599</v>
+        <v>2.3351</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.3351</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.4599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. DENG</t>
+          <t>M. AMADASUN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7329</v>
+        <v>1.3463</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5311</v>
+        <v>0.1731</v>
       </c>
       <c r="F19" t="n">
-        <v>2.264</v>
+        <v>1.1732</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.2025</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.7208</v>
+        <v>0.0254</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4817</v>
+        <v>0.0572</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.5737</v>
+        <v>0.7156</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.5165</v>
+        <v>0.5196</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0572</v>
+        <v>0.1959</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6289</v>
+        <v>-0.633</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2043</v>
+        <v>-0.4942</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4245</v>
+        <v>-0.1388</v>
       </c>
       <c r="P19" t="n">
-        <v>1.2487</v>
+        <v>0.6244</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2893</v>
+        <v>2.7055</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3517</v>
+        <v>1.577</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2519</v>
+        <v>1.3088</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6035</v>
+        <v>0.2682</v>
       </c>
       <c r="V19" t="n">
-        <v>2.3351</v>
+        <v>-0.9376</v>
       </c>
       <c r="W19" t="n">
-        <v>2.3351</v>
+        <v>0.23</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. CEBOLLA PORCAR</t>
+          <t>G. MCKAY JR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5573</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6859</v>
+        <v>-1.3284</v>
       </c>
       <c r="F20" t="n">
-        <v>2.2432</v>
+        <v>1.3941</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.2256</v>
+        <v>-0.3535</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.3481</v>
+        <v>-0.3902</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1225</v>
+        <v>0.0367</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.1234</v>
+        <v>-0.676</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.5275</v>
+        <v>-0.676</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4041</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1022</v>
+        <v>0.3225</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1794</v>
+        <v>0.2857</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2817</v>
+        <v>0.0367</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2081</v>
+        <v>1.0406</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8731</v>
+        <v>1.0406</v>
       </c>
       <c r="S20" t="n">
-        <v>2.3636</v>
+        <v>-0.3915</v>
       </c>
       <c r="T20" t="n">
-        <v>1.8912</v>
+        <v>-0.6524</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4724</v>
+        <v>0.261</v>
       </c>
       <c r="V20" t="n">
-        <v>1.6275</v>
+        <v>-0.23</v>
       </c>
       <c r="W20" t="n">
-        <v>1.6275</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. MCKAY JR</t>
+          <t>J. LLAMAS PRADO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0518</v>
+        <v>-0.2132</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3284</v>
+        <v>-1.2549</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2767</v>
+        <v>1.0417</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3535</v>
+        <v>-0.3572</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3902</v>
+        <v>-1.6782</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0367</v>
+        <v>1.321</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.676</v>
+        <v>-0.402</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.676</v>
+        <v>-2.1475</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.7455</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3225</v>
+        <v>0.0448</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2857</v>
+        <v>0.4693</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0367</v>
+        <v>-0.4245</v>
       </c>
       <c r="P21" t="n">
-        <v>1.0406</v>
+        <v>2.2893</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0406</v>
+        <v>2.2893</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5089</v>
+        <v>-0.7478</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6524</v>
+        <v>-0.8529</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1435</v>
+        <v>0.1051</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.23</v>
+        <v>-1.3975</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.23</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. LLAMAS PRADO</t>
+          <t>D. CEBOLLA PORCAR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4721</v>
+        <v>-0.2642</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5764</v>
+        <v>-2.6503</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1043</v>
+        <v>2.3861</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3572</v>
+        <v>-3.2256</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6782</v>
+        <v>-3.3481</v>
       </c>
       <c r="I22" t="n">
-        <v>1.321</v>
+        <v>0.1225</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.402</v>
+        <v>-3.1234</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.1475</v>
+        <v>-3.5275</v>
       </c>
       <c r="L22" t="n">
-        <v>1.7455</v>
+        <v>0.4041</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0448</v>
+        <v>-0.1022</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4693</v>
+        <v>0.1794</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4245</v>
+        <v>-0.2817</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2893</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2893</v>
+        <v>1.8731</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0066</v>
+        <v>1.5421</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1744</v>
+        <v>0.9268</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1677</v>
+        <v>0.6153</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.3975</v>
+        <v>1.6275</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.6275</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.3975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4026</v>
+        <v>-1.9344</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.1613</v>
+        <v>-3.8398</v>
       </c>
       <c r="F23" t="n">
-        <v>1.7587</v>
+        <v>1.9055</v>
       </c>
       <c r="G23" t="n">
         <v>-2.7334</v>
@@ -2248,13 +2248,13 @@
         <v>0.8325</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5017</v>
+        <v>-0.0334</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7829</v>
+        <v>-0.4615</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2812</v>
+        <v>0.428</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>18.462</v>
+        <v>19.8907</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.076899999999999</v>
+        <v>-1.077100000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>19.5391</v>
+        <v>20.9679</v>
       </c>
       <c r="G24" t="n">
         <v>-1.999600000000001</v>
@@ -2302,46 +2302,46 @@
         <v>-2.774000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>-7.733700000000001</v>
+        <v>-7.7337</v>
       </c>
       <c r="L24" t="n">
-        <v>4.9596</v>
+        <v>4.959599999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7743000000000002</v>
+        <v>0.7743000000000001</v>
       </c>
       <c r="N24" t="n">
         <v>1.1008</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3265</v>
+        <v>-0.3265000000000001</v>
       </c>
       <c r="P24" t="n">
         <v>14.5683</v>
       </c>
       <c r="Q24" t="n">
-        <v>-7.2842</v>
+        <v>-7.284199999999999</v>
       </c>
       <c r="R24" t="n">
         <v>21.8524</v>
       </c>
       <c r="S24" t="n">
-        <v>2.391</v>
+        <v>3.8197</v>
       </c>
       <c r="T24" t="n">
-        <v>0.01239999999999941</v>
+        <v>0.0126</v>
       </c>
       <c r="U24" t="n">
-        <v>2.3783</v>
+        <v>3.807199999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>3.5026</v>
+        <v>3.502600000000001</v>
       </c>
       <c r="W24" t="n">
-        <v>8.968800000000002</v>
+        <v>8.9688</v>
       </c>
       <c r="X24" t="n">
-        <v>-5.466100000000001</v>
+        <v>-5.4661</v>
       </c>
     </row>
   </sheetData>
